--- a/output/solution_metadata.xlsx
+++ b/output/solution_metadata.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>386548.2649</t>
+          <t>3.0000</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>7.70</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>386548.2649</t>
+          <t>3.0000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>386548.2649</t>
+          <t>3.0000</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>386548.2649</t>
+          <t>3.0127</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>386548.2649</t>
+          <t>2.9740</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
